--- a/Build_list.xlsx
+++ b/Build_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,23 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>TS3_note.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SS_mapping.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SS_note.xlsx</t>
         </is>
       </c>
     </row>

--- a/Build_list.xlsx
+++ b/Build_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6O</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6O_mapping.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6O_note.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Build_list.xlsx
+++ b/Build_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,23 +515,6 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>SS_note.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6O</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6O_mapping.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6O_note.xlsx</t>
         </is>
       </c>
     </row>
